--- a/survey_templates/044_mental_health_service_assessment_form--survey_templates.xlsx
+++ b/survey_templates/044_mental_health_service_assessment_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mental_health_service_goals</t>
+          <t>mental_health_service_goals_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mental Health Service Goals</t>
+          <t>Mental Health Service Goals 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mental_health_service_outcome</t>
+          <t>mental_health_service_outcome_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mental Health Service Outcome</t>
+          <t>Mental Health Service Outcome 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mental_health_service_outcome</t>
+          <t>mental_health_service_outcome_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mental Health Service Outcome</t>
+          <t>Mental Health Service Outcome 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -802,7 +802,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -861,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mental_health_service_goals_choices</t>
+          <t>mental_health_service_goals_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mental_health_service_goals_choices</t>
+          <t>mental_health_service_goals_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mental_health_service_outcome_choices</t>
+          <t>mental_health_service_outcome_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mental_health_service_outcome_choices</t>
+          <t>mental_health_service_outcome_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
